--- a/artfynd/A 605-2024 artfynd.xlsx
+++ b/artfynd/A 605-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>117704560</v>
       </c>
       <c r="B3" t="n">
-        <v>57999</v>
+        <v>58000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>117704126</v>
       </c>
       <c r="B4" t="n">
-        <v>57620</v>
+        <v>57621</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 605-2024 artfynd.xlsx
+++ b/artfynd/A 605-2024 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>117704560</v>
       </c>
       <c r="B4" t="n">
-        <v>58192</v>
+        <v>58195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
